--- a/src/main/kotlin/com/kcvn/spm/assets/template/ImportInventoryProductTemplate.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/ImportInventoryProductTemplate.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
-    <sheet name="Data" sheetId="1" r:id="rId1"/>
+    <sheet name="Tồn kho file" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -19,14 +19,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Số lớp</t>
   </si>
   <si>
-    <t>Mã công đoạn</t>
-  </si>
-  <si>
     <t>Số quản lý</t>
   </si>
   <si>
@@ -39,13 +36,40 @@
     <t>Tên sản phẩm KC</t>
   </si>
   <si>
+    <t>Tên công đoạn</t>
+  </si>
+  <si>
+    <t>Mã nhân viên</t>
+  </si>
+  <si>
+    <t>Mã Công đoạn</t>
+  </si>
+  <si>
+    <t>Chỉ thị xử lý</t>
+  </si>
+  <si>
+    <t>Số chiếc / một tấm sản phẩm</t>
+  </si>
+  <si>
+    <t>Tên khu vực sản xuất</t>
+  </si>
+  <si>
+    <t>Số lượng tiến trình</t>
+  </si>
+  <si>
+    <t>Đội:</t>
+  </si>
+  <si>
+    <t>Process name(JP)</t>
+  </si>
+  <si>
     <t>Số tấm thành phẩm</t>
   </si>
   <si>
     <t>Số tấm nguyên liệu</t>
   </si>
   <si>
-    <t>Tên công đoạn</t>
+    <t>Số đại diện Seiden</t>
   </si>
 </sst>
 </file>
@@ -74,12 +98,18 @@
       <family val="1"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="2">
@@ -91,17 +121,17 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color indexed="64"/>
+      <left style="medium">
+        <color rgb="FFCCCCCC"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
       </right>
-      <top style="thin">
-        <color indexed="64"/>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
       </top>
-      <bottom style="thin">
-        <color indexed="64"/>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
       </bottom>
       <diagonal/>
     </border>
@@ -109,12 +139,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -397,59 +430,77 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:Z1"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="28.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.28515625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="22.140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.85546875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="21.5703125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="19.85546875" style="1" customWidth="1"/>
-    <col min="7" max="7" width="24.7109375" style="1" customWidth="1"/>
-    <col min="8" max="8" width="24.28515625" style="1" customWidth="1"/>
-    <col min="9" max="9" width="18" style="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" customWidth="1"/>
-    <col min="12" max="13" width="15" style="1" customWidth="1"/>
-    <col min="14" max="14" width="16" style="1" customWidth="1"/>
-    <col min="15" max="15" width="17.85546875" style="1" customWidth="1"/>
-    <col min="16" max="16" width="16.7109375" style="1" customWidth="1"/>
-    <col min="17" max="17" width="11.140625" style="1" customWidth="1"/>
+    <col min="1" max="17" width="24" style="1" customWidth="1"/>
     <col min="18" max="18" width="10" style="1" customWidth="1"/>
     <col min="19" max="19" width="11" style="1" customWidth="1"/>
     <col min="20" max="20" width="11.7109375" style="1" customWidth="1"/>
     <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:26" s="2" customFormat="1" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F1" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="G1" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C1" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="J1" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="K1" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>7</v>
-      </c>
+      <c r="M1" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="O1" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="3"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
+      <c r="U1" s="3"/>
+      <c r="V1" s="3"/>
+      <c r="W1" s="3"/>
+      <c r="X1" s="3"/>
+      <c r="Y1" s="3"/>
+      <c r="Z1" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/src/main/kotlin/com/kcvn/spm/assets/template/ImportInventoryProductTemplate.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/ImportInventoryProductTemplate.xlsx
@@ -139,7 +139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -149,6 +149,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -433,7 +439,9 @@
   <dimension ref="A1:Z1"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="17" width="24" style="1" customWidth="1"/>
+    <col min="1" max="5" width="24" style="1" customWidth="1"/>
+    <col min="6" max="6" width="24" style="5" customWidth="1"/>
+    <col min="7" max="17" width="24" style="1" customWidth="1"/>
     <col min="18" max="18" width="10" style="1" customWidth="1"/>
     <col min="19" max="19" width="11" style="1" customWidth="1"/>
     <col min="20" max="20" width="11.7109375" style="1" customWidth="1"/>
@@ -456,7 +464,7 @@
       <c r="E1" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="G1" s="3" t="s">

--- a/src/main/kotlin/com/kcvn/spm/assets/template/ImportInventoryProductTemplate.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/ImportInventoryProductTemplate.xlsx
@@ -57,9 +57,6 @@
     <t>Số lượng tiến trình</t>
   </si>
   <si>
-    <t>Đội:</t>
-  </si>
-  <si>
     <t>Process name(JP)</t>
   </si>
   <si>
@@ -70,6 +67,9 @@
   </si>
   <si>
     <t>Số đại diện Seiden</t>
+  </si>
+  <si>
+    <t>Đội</t>
   </si>
 </sst>
 </file>
@@ -453,7 +453,7 @@
         <v>6</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="C1" s="3" t="s">
         <v>7</v>
@@ -462,7 +462,7 @@
         <v>5</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="F1" s="4" t="s">
         <v>1</v>
@@ -492,13 +492,13 @@
         <v>11</v>
       </c>
       <c r="O1" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="P1" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>15</v>
-      </c>
-      <c r="Q1" s="3" t="s">
-        <v>16</v>
       </c>
       <c r="R1" s="3"/>
       <c r="S1" s="3"/>

--- a/src/main/kotlin/com/kcvn/spm/assets/template/ImportInventoryProductTemplate.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/ImportInventoryProductTemplate.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
   <si>
     <t>Số lớp</t>
   </si>
@@ -70,6 +70,12 @@
   </si>
   <si>
     <t>Đội</t>
+  </si>
+  <si>
+    <t>Số tấm thành phẩm OK</t>
+  </si>
+  <si>
+    <t>KTNQ 30 NGAY</t>
   </si>
 </sst>
 </file>
@@ -112,7 +118,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -135,11 +141,39 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="medium">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -150,11 +184,17 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -440,69 +480,73 @@
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="5" width="24" style="1" customWidth="1"/>
-    <col min="6" max="6" width="24" style="5" customWidth="1"/>
+    <col min="6" max="6" width="24" style="4" customWidth="1"/>
     <col min="7" max="17" width="24" style="1" customWidth="1"/>
-    <col min="18" max="18" width="10" style="1" customWidth="1"/>
-    <col min="19" max="19" width="11" style="1" customWidth="1"/>
+    <col min="18" max="18" width="27.5703125" style="1" customWidth="1"/>
+    <col min="19" max="19" width="23.28515625" style="1" customWidth="1"/>
     <col min="20" max="20" width="11.7109375" style="1" customWidth="1"/>
     <col min="21" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" s="2" customFormat="1" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="6" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="6" t="s">
         <v>2</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="6" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
+      <c r="R1" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="5"/>
       <c r="U1" s="3"/>
       <c r="V1" s="3"/>
       <c r="W1" s="3"/>

--- a/src/main/kotlin/com/kcvn/spm/assets/template/ImportInventoryProductTemplate.xlsx
+++ b/src/main/kotlin/com/kcvn/spm/assets/template/ImportInventoryProductTemplate.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
   <si>
     <t>Số lớp</t>
   </si>
@@ -70,12 +70,6 @@
   </si>
   <si>
     <t>Đội</t>
-  </si>
-  <si>
-    <t>Số tấm thành phẩm OK</t>
-  </si>
-  <si>
-    <t>KTNQ 30 NGAY</t>
   </si>
 </sst>
 </file>
@@ -476,19 +470,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:Z1"/>
+  <dimension ref="A1:X1"/>
   <sheetFormatPr defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="5" width="24" style="1" customWidth="1"/>
     <col min="6" max="6" width="24" style="4" customWidth="1"/>
     <col min="7" max="17" width="24" style="1" customWidth="1"/>
-    <col min="18" max="18" width="27.5703125" style="1" customWidth="1"/>
-    <col min="19" max="19" width="23.28515625" style="1" customWidth="1"/>
-    <col min="20" max="20" width="11.7109375" style="1" customWidth="1"/>
-    <col min="21" max="16384" width="9.140625" style="1"/>
+    <col min="18" max="18" width="11.7109375" style="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" s="2" customFormat="1" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" s="2" customFormat="1" ht="31.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="6" t="s">
         <v>6</v>
       </c>
@@ -540,19 +532,13 @@
       <c r="Q1" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="6" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" s="6" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" s="5"/>
+      <c r="R1" s="5"/>
+      <c r="S1" s="3"/>
+      <c r="T1" s="3"/>
       <c r="U1" s="3"/>
       <c r="V1" s="3"/>
       <c r="W1" s="3"/>
       <c r="X1" s="3"/>
-      <c r="Y1" s="3"/>
-      <c r="Z1" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
